--- a/Assmnt1_car_rental/Car_rental.xlsx
+++ b/Assmnt1_car_rental/Car_rental.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTMAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4b553712466eeafb/Documents/GitHub/MS008/Assmnt1_car_rental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9647988F-06F8-459C-AA8C-28BCDDA4B972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9647988F-06F8-459C-AA8C-28BCDDA4B972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7DA5AF-38DE-4C17-9ED5-B60ED3FE15AB}"/>
   <bookViews>
-    <workbookView xWindow="12132" yWindow="960" windowWidth="8868" windowHeight="9960" xr2:uid="{7637FAFC-6C16-44C5-B346-C1F6F827C461}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7637FAFC-6C16-44C5-B346-C1F6F827C461}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>booked_yn</t>
   </si>
@@ -99,6 +99,126 @@
   </si>
   <si>
     <t>When a customer returns the rented car, it will have the following status:</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>1 Admin User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Customer </t>
+  </si>
+  <si>
+    <t>3. Exit</t>
+  </si>
+  <si>
+    <t>Select an option:</t>
+  </si>
+  <si>
+    <t>Option 2 Member Menu:</t>
+  </si>
+  <si>
+    <t>--&gt; Customer login page:</t>
+  </si>
+  <si>
+    <t>enter username:</t>
+  </si>
+  <si>
+    <t>enter password</t>
+  </si>
+  <si>
+    <t>--&gt; Customer Menu</t>
+  </si>
+  <si>
+    <t>1. Update customer details *when logged in, the user can change his personal info</t>
+  </si>
+  <si>
+    <t>2. View your rental history *view car rental history by username</t>
+  </si>
+  <si>
+    <t>3. View Cars * view all car in the database</t>
+  </si>
+  <si>
+    <t>4. Book a Car</t>
+  </si>
+  <si>
+    <t>5. Make Payment</t>
+  </si>
+  <si>
+    <t>6. Return to Main Menu</t>
+  </si>
+  <si>
+    <t>Option 4:</t>
+  </si>
+  <si>
+    <t>car_id</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>plate_number</t>
+  </si>
+  <si>
+    <t>colour</t>
+  </si>
+  <si>
+    <t>max_passenger</t>
+  </si>
+  <si>
+    <t>daily_rate</t>
+  </si>
+  <si>
+    <t>Option 6 Book a car:</t>
+  </si>
+  <si>
+    <t>Rental Date Start (DD/MM/YYYY):</t>
+  </si>
+  <si>
+    <t>Rental Date End (DD/MM/YYYY):</t>
+  </si>
+  <si>
+    <t>Enter car_id:</t>
+  </si>
+  <si>
+    <t>After that display the following confirmation:</t>
+  </si>
+  <si>
+    <t>Rate per Day (NZD):</t>
+  </si>
+  <si>
+    <t>Total rent Amount (NZD):</t>
+  </si>
+  <si>
+    <t>Booked by: *should be username of customer*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please confirm Booking (y/N): </t>
+  </si>
+  <si>
+    <t>Booking saved, please proceed to payments!</t>
+  </si>
+  <si>
+    <t>Option 5 Make Payment:</t>
+  </si>
+  <si>
+    <t>Name on Card:</t>
+  </si>
+  <si>
+    <t>Enter Card Number: 16 digit</t>
+  </si>
+  <si>
+    <t>Enter Card Expiry: (DD/MM/YYYY)</t>
+  </si>
+  <si>
+    <t>Enter Card Type: Cash or CC</t>
+  </si>
+  <si>
+    <t>* Payment accepted, Booking confirmed!</t>
   </si>
 </sst>
 </file>
@@ -478,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9092E5-8137-449B-92F0-DC8BF9ED47A3}">
-  <dimension ref="A5:F28"/>
+  <dimension ref="A5:F95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -676,6 +796,256 @@
         <v>3</v>
       </c>
     </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
